--- a/docs/PP_Feature_Analysis.xlsx
+++ b/docs/PP_Feature_Analysis.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project-pulse\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ADF0EA-8676-4297-8512-C2A68656FB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01BA0F4-D884-4FE5-833B-9422BD8D3AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8B3404AF-7916-404A-8A1E-1D8040A382EE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{8B3404AF-7916-404A-8A1E-1D8040A382EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$12</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="85">
   <si>
     <t>Column</t>
   </si>
@@ -54,9 +58,6 @@
     <t>Unique YouTube-generated identifier for each video.</t>
   </si>
   <si>
-    <t>❌ No</t>
-  </si>
-  <si>
     <t>Generated by YouTube during upload. Contains no meaningful information for predicting views and serves only as a unique identifier.</t>
   </si>
   <si>
@@ -66,17 +67,243 @@
     <t>The title entered by the creator while publishing the video. It is visible to viewers and may differ from the original video filename.</t>
   </si>
   <si>
-    <t>✅ Yes</t>
-  </si>
-  <si>
     <t>Titles influence viewer interest and click behavior. Later they can be transformed into useful text-based features for machine learning.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Date and time the video was published on YouTube.</t>
+  </si>
+  <si>
+    <t>Publishing date and time can influence video performance (day, month, hour, weekday, season) and can later be engineered into useful predictive features.</t>
+  </si>
+  <si>
+    <t>Yes*</t>
+  </si>
+  <si>
+    <t>Technically, the actual publish timestamp is generated only when the video is published. However, the creator knows the planned or scheduled publish date and time before publishing. Since Project Pulse predicts performance before publishing, this feature is considered available at prediction time.</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Video duration can significantly influence viewer retention, watch time, and overall performance, making it an important pre-publish predictive feature.</t>
+  </si>
+  <si>
+    <t>Length of the video in seconds.</t>
+  </si>
+  <si>
+    <t>Subscribers gained</t>
+  </si>
+  <si>
+    <t>Total number of people who subscribed to the channel after watching the video</t>
+  </si>
+  <si>
+    <t>Subscribers gained is generated only after the video is published and strongly correlates with video performance, making it a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Subscribers lost</t>
+  </si>
+  <si>
+    <t>Total number of people who unsubscribed to the channel after watching the video</t>
+  </si>
+  <si>
+    <t>Subscribers lost is generated only after the video is published and reflects audience response, making it a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Likes</t>
+  </si>
+  <si>
+    <t>Dislikes</t>
+  </si>
+  <si>
+    <t>Total number of likes received by the video.</t>
+  </si>
+  <si>
+    <t>Total number of dislikes received by the video.</t>
+  </si>
+  <si>
+    <t>Likes are generated only after the video is published and strongly reflect audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Dislikes are generated only after the video is published and reflect audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Likes (vs dislikes) (%)</t>
+  </si>
+  <si>
+    <t>This metric is calculated from audience reactions after the video is published and therefore leaks post-publish engagement information.</t>
+  </si>
+  <si>
+    <t>Percentage of likes relative to total likes and dislikes.</t>
+  </si>
+  <si>
+    <t>Shares</t>
+  </si>
+  <si>
+    <t>Total number of times the video was shared by viewers.</t>
+  </si>
+  <si>
+    <t>Shares are generated only after the video is published and indicate audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments added </t>
+  </si>
+  <si>
+    <t>Total number of comments posted on the video.</t>
+  </si>
+  <si>
+    <t>Comments are generated only after the video is published and reflect audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Hypes</t>
+  </si>
+  <si>
+    <t>Views</t>
+  </si>
+  <si>
+    <t>Subscribers</t>
+  </si>
+  <si>
+    <t>Impressions</t>
+  </si>
+  <si>
+    <t>Impressions are generated only after the video is published because YouTube decides how many users to show the video to. They therefore leak post-publish platform behavior.</t>
+  </si>
+  <si>
+    <t>Impression CTR is calculated from impressions and user clicks after publishing. It reflects post-publish audience behavior and is therefore a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Remix Count</t>
+  </si>
+  <si>
+    <t>Total number of remixes created using the video.</t>
+  </si>
+  <si>
+    <t>Remix count is generated only after the video is published and reflects audience interaction, making it a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Remix Views</t>
+  </si>
+  <si>
+    <t>Total number of views received by videos remixed from the original video.</t>
+  </si>
+  <si>
+    <t>Remix views are generated only after publishing and depend on audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Engaged Views</t>
+  </si>
+  <si>
+    <t>Total number of engaged views received by the video. YouTube determines engaged views using factors such as viewer retention, watch behavior, likes, comments, shares, and other engagement signals. Engaged views are used for monetization and other platform benefits.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Target Candidate)</t>
+    </r>
+  </si>
+  <si>
+    <t>Engaged views are calculated only after publishing using audience behavior and platform signals, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Average View Duration</t>
+  </si>
+  <si>
+    <t>Average amount of time viewers watched the video.</t>
+  </si>
+  <si>
+    <t>Average view duration is calculated only after the video is published and reflects audience retention, making it a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Average Percentage Viewed (%)</t>
+  </si>
+  <si>
+    <t>Average percentage of the video watched relative to its total duration.</t>
+  </si>
+  <si>
+    <t>This metric is calculated after publishing using viewer watch behavior and therefore leaks post-publish engagement information.</t>
+  </si>
+  <si>
+    <t>Stayed to Watch (%)</t>
+  </si>
+  <si>
+    <t>Percentage of viewers who were shown the Short in the feed and chose to stop and watch it (engaged view).</t>
+  </si>
+  <si>
+    <t>This metric depends on viewer behavior after publishing and is therefore a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Total number of Hypes received by the video.</t>
+  </si>
+  <si>
+    <t>Hypes are received only after the video is published and represent audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Hype Points</t>
+  </si>
+  <si>
+    <t>Total number of Hype points received by the video.</t>
+  </si>
+  <si>
+    <t>Hype points are generated only after publishing and reflect audience engagement, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Total number of views received by the video, including both engaged and unengaged views.</t>
+  </si>
+  <si>
+    <t>Views are generated only after publishing and represent the target outcome being predicted, making them a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Watch Time (Hours)</t>
+  </si>
+  <si>
+    <t>Total watch time accumulated by the video in hours.</t>
+  </si>
+  <si>
+    <t>Watch time is accumulated only after the video is published and therefore leaks post-publish audience behavior.</t>
+  </si>
+  <si>
+    <t>Net subscribers gained from the video (Subscribers Gained − Subscribers Lost).</t>
+  </si>
+  <si>
+    <t>Net subscribers are calculated only after publishing based on audience response, making this a data leakage feature.</t>
+  </si>
+  <si>
+    <t>Total number of times YouTube showed the video to viewers in the Shorts feed or other surfaces.</t>
+  </si>
+  <si>
+    <t>Impressions Click-Through Rate (%)</t>
+  </si>
+  <si>
+    <t>Percentage of impressions that resulted in a viewer clicking or watching the video.</t>
+  </si>
+  <si>
+    <t>Video publish time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +313,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -113,13 +348,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,8 +677,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E0F22D-BDAC-4AB1-89BF-E8FAB3B0C436}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="130.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -461,50 +711,579 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="109.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="106.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B76689B7-A7C2-40F9-A7AE-402D36CBEB7E}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
